--- a/feedback_forms/012_onboarding_feedback_questionnaire--feedback_forms.xlsx
+++ b/feedback_forms/012_onboarding_feedback_questionnaire--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire</t>
+          <t>onboarding_first_impressions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire</t>
+          <t>What were your first impressions of our company culture?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>feedback_questions</t>
+          <t>onboarding_process</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feedback_questions</t>
+          <t>How did you feel about the onboarding process?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>open_ended_questions</t>
+          <t>onboarding_expectations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>open_ended_questions</t>
+          <t>What were your expectations before joining the company, and how were they met?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>feedback_manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>Who would you like to give feedback to about your onboarding experience?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>onboarding_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>Rate your overall experience with the onboarding process.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>department_id</t>
+          <t>feedback_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>department_id</t>
+          <t>How frequently do you give feedback to your manager?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>manager_id</t>
+          <t>next_steps</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manager_id</t>
+          <t>What actions would you like to see taken as a result of your feedback?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>onboarding_length</t>
+          <t>What are your thoughts on the length of the onboarding process?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>onboarding_date</t>
+          <t>What is your onboarding date?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>manager_score</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>Rate your satisfaction with your manager's feedback.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>feedback_score</t>
+          <t>employee_score</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feedback_score</t>
+          <t>Rate your satisfaction with your own feedback.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>manager_score</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>manager_score</t>
+          <t>How satisfied are you with your overall experience on the company?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>employee_score</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>employee_score</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>overall_experience</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>overall_experience</t>
+          <t>How frequently do you use email to give feedback?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>overall_experience_comments</t>
+          <t>email_comments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>overall_experience_comments</t>
+          <t>What are your comments on email?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>feedback_frequency</t>
+          <t>manager_name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feedback_frequency</t>
+          <t>What is your manager's name?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>feedback_source</t>
+          <t>manager_name_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feedback_source</t>
+          <t>How would you rate the length of time you have spent onboarding?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>manager_name_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Manager Name 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>manager_name_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Manager Name 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>next_steps_actions</t>
+          <t>manager_name_5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>next_steps_actions</t>
+          <t>What are your comments on your onboarding experience with your manager?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,17 +975,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>onboarding_length_comments</t>
+          <t>onboarding_length_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>onboarding_length_comments</t>
+          <t>What is your onboarding length?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +998,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>onboarding_date_comments</t>
+          <t>manager_name_6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>onboarding_date_comments</t>
+          <t>Manager Name 6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>onboarding_length</t>
+          <t>email_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>onboarding_length</t>
+          <t>Email 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,17 +1044,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>email_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>Email 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,17 +1067,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>overall_experience</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>overall_experience</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,170 +1126,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'manager_1'}</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 1'}</t>
+          <t>Manager 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'manager_2'}</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 2'}</t>
+          <t>Manager 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'manager_3'}</t>
+          <t>manager_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 3'}</t>
+          <t>Manager 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'manager_4'}</t>
+          <t>manager_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 4'}</t>
+          <t>Manager 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'manager_5'}</t>
+          <t>manager_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 5'}</t>
+          <t>Manager 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>onboarding_experience_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>onboarding_experience_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>onboarding_experience_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neither_satisfied_nor_unsatisfied'}</t>
+          <t>neither_satisfied_nor_unsatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Satisfied nor Unsatisfied'}</t>
+          <t>Neither Satisfied nor Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>onboarding_experience_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unsatisfied'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unsatisfied'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>onboarding_experience_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_unsatisfied'}</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unsatisfied'}</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1352,267 +1352,267 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>send_email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Send email</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>feedback_source_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>create_task</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Create task</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>feedback_source_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'chat'}</t>
+          <t>create_issue</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Chat'}</t>
+          <t>Create issue</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>feedback_source_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>feedback_source_choices</t>
+          <t>manager_score_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'In-Person'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>feedback_source_choices</t>
+          <t>manager_score_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>next_steps_actions_choices</t>
+          <t>manager_score_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'send_email'}</t>
+          <t>neither_satisfied_nor_unsatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Send email'}</t>
+          <t>Neither Satisfied nor Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>next_steps_actions_choices</t>
+          <t>manager_score_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'create_task'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Create task'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>next_steps_actions_choices</t>
+          <t>manager_score_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'create_issue'}</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Create issue'}</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>next_steps_actions_choices</t>
+          <t>employee_score_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>employee_score_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'manager_1'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 1'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>employee_score_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'manager_2'}</t>
+          <t>neither_satisfied_nor_unsatisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 2'}</t>
+          <t>Neither Satisfied nor Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>employee_score_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'manager_3'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 3'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>employee_score_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'manager_4'}</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 4'}</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>manager_name_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'manager_5'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Manager 5'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>neither_satisfied_nor_unsatisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Neither Satisfied nor Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'neither_satisfied_nor_unsatisfied'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Satisfied nor Unsatisfied'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,335 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unsatisfied'}</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unsatisfied'}</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>email_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'very_unsatisfied'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unsatisfied'}</t>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>email_2_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>email_2_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>frequently</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Frequently</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>email_2_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>manager_name_3_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>manager_1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Manager 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>manager_name_3_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>manager_2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Manager 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>manager_name_3_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>manager_3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Manager 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>manager_name_3_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>manager_4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Manager 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>manager_name_3_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>manager_5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Manager 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>manager_name_4_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>manager_name_4_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>manager_name_4_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Neither Satisfied nor Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>manager_name_4_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>somewhat_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Somewhat Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>manager_name_4_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>very_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Very Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>manager_name_6_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>manager_name_6_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>manager_name_6_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Neither Satisfied nor Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>manager_name_6_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>somewhat_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Somewhat Unsatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>manager_name_6_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>very_unsatisfied</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
